--- a/ML_macroed.xlsx
+++ b/ML_macroed.xlsx
@@ -768,522 +768,626 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali che guidano/strutturano attività</t>
+          <t>materiali/strumenti fisici
+materiali che guidano/strutturano attività</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- robot</t>
+          <t>materiali/strumenti fisici
+robot</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- cancelleria/uso comune</t>
+          <t>materiali/strumenti fisici
+cancelleria/uso comune</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali che guidano/strutturano attività</t>
+          <t>materiali/strumenti fisici
+materiali che guidano/strutturano attività</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- corpo</t>
+          <t>materiali/strumenti fisici
+corpo</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- pc/tablet</t>
+          <t>materiali/strumenti fisici
+pc/tablet</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- lim</t>
+          <t>materiali/strumenti fisici
+lim</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- corpo</t>
+          <t>materiali/strumenti fisici
+corpo</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- cancelleria/uso comune</t>
+          <t>materiali/strumenti fisici
+cancelleria/uso comune</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- corpo</t>
+          <t>materiali/strumenti fisici
+corpo</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali di ambiente/movimento in cui si opera per le attività</t>
+          <t>materiali/strumenti fisici
+materiali di ambiente/movimento in cui si opera per le attività</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- cancelleria/uso comune</t>
+          <t>materiali/strumenti fisici
+cancelleria/uso comune</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- carte/blocchi</t>
+          <t>materiali/strumenti fisici
+carte/blocchi</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali di ambiente/movimento in cui si opera per le attività</t>
+          <t>materiali/strumenti fisici
+materiali di ambiente/movimento in cui si opera per le attività</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- cancelleria/uso comune</t>
+          <t>materiali/strumenti fisici
+cancelleria/uso comune</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali che guidano/strutturano attività</t>
+          <t>materiali/strumenti fisici
+materiali che guidano/strutturano attività</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- cancelleria/uso comune</t>
+          <t>materiali/strumenti fisici
+cancelleria/uso comune</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali che guidano/strutturano attività</t>
+          <t>materiali/strumenti fisici
+materiali che guidano/strutturano attività</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali di ambiente/movimento in cui si opera per le attività</t>
+          <t>materiali/strumenti fisici
+materiali di ambiente/movimento in cui si opera per le attività</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>attività -- costrutti di base</t>
+          <t>attività
+costrutti di base</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>attività -- costrutti di base</t>
+          <t>attività
+costrutti di base</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>attività -- costrutti di base</t>
+          <t>attività
+costrutti di base</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>attività -- altro</t>
+          <t>attività
+altro</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>attività -- contenuti algoritmici</t>
+          <t>attività
+contenuti algoritmici</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>attività -- movimento e percorsi</t>
+          <t>attività
+movimento e percorsi</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>materiali/strumenti fisici -- materiali che guidano/strutturano attività</t>
+          <t>materiali/strumenti fisici
+materiali che guidano/strutturano attività</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>attività -- videogiochi</t>
+          <t>attività
+videogiochi</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>attività -- contenuti algoritmici</t>
+          <t>attività
+contenuti algoritmici</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>attività -- uso tecnologia e sviluppo contenuti</t>
+          <t>attività
+uso tecnologia e sviluppo contenuti</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>attività -- storytelling</t>
+          <t>attività
+storytelling</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>attività -- unplugged</t>
+          <t>attività
+unplugged</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>attività -- unplugged</t>
+          <t>attività
+unplugged</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>attività -- processi di informatica</t>
+          <t>attività
+processi di informatica</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>attività -- processi di informatica</t>
+          <t>attività
+processi di informatica</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>attività -- verifica e correzione</t>
+          <t>attività
+verifica e correzione</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>attività -- uso tecnologia e sviluppo contenuti</t>
+          <t>attività
+uso tecnologia e sviluppo contenuti</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>attività -- pixel art</t>
+          <t>attività
+pixel art</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>attività -- costrutti di base</t>
+          <t>attività
+costrutti di base</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>attività -- programmazione</t>
+          <t>attività
+programmazione</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>attività -- coding</t>
+          <t>attività
+coding</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>attività -- altro</t>
+          <t>attività
+altro</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>attività -- uso tecnologia e sviluppo contenuti</t>
+          <t>attività
+uso tecnologia e sviluppo contenuti</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>attività -- movimento e percorsi</t>
+          <t>attività
+movimento e percorsi</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>attività -- processi di informatica</t>
+          <t>attività
+processi di informatica</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>attività -- contenuti algoritmici</t>
+          <t>attività
+contenuti algoritmici</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>attività -- contenuti algoritmici</t>
+          <t>attività
+contenuti algoritmici</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>attività -- costrutti di base</t>
+          <t>attività
+costrutti di base</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>attività -- processi di informatica</t>
+          <t>attività
+processi di informatica</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>attività -- movimento e percorsi</t>
+          <t>attività
+movimento e percorsi</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>attività -- unplugged</t>
+          <t>attività
+unplugged</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- intelligenza artificiale</t>
+          <t>obiettivi disciplinari
+intelligenza artificiale</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>attività -- strumentali per altre discipline</t>
+          <t>attività
+strumentali per altre discipline</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività</t>
+          <t>soft skills/ trasversali/ metacognizione
+creatività</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- spazialità</t>
+          <t>interdisciplinarità
+spazialità</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- geografia</t>
+          <t>interdisciplinarità
+geografia</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- geografia</t>
+          <t>interdisciplinarità
+geografia</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- spazialità</t>
+          <t>interdisciplinarità
+spazialità</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- software di creazione/ricerca contenuti</t>
+          <t>piattaforma/ ambiente
+software di creazione/ricerca contenuti</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- ambiente pixel art</t>
+          <t>piattaforma/ ambiente
+ambiente pixel art</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- software di creazione/ricerca contenuti</t>
+          <t>piattaforma/ ambiente
+software di creazione/ricerca contenuti</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- scratch</t>
+          <t>piattaforma/ ambiente
+scratch</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- geometria dinamica</t>
+          <t>piattaforma/ ambiente
+geometria dinamica</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- code.org / programma il futuro</t>
+          <t>piattaforma/ ambiente
+code.org / programma il futuro</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- google workspace</t>
+          <t>piattaforma/ ambiente
+google workspace</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- code.org / programma il futuro</t>
+          <t>piattaforma/ ambiente
+code.org / programma il futuro</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- software di creazione/ricerca contenuti</t>
+          <t>piattaforma/ ambiente
+software di creazione/ricerca contenuti</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- carte/blocchi programmazione</t>
+          <t>piattaforma/ ambiente
+carte/blocchi programmazione</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- robot</t>
+          <t>piattaforma/ ambiente
+robot</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>piattaforma/ ambiente -- software di creazione/ricerca contenuti</t>
+          <t>piattaforma/ ambiente
+software di creazione/ricerca contenuti</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>metodologia -- sì</t>
+          <t>metodologia
+sì</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>metodologia -- forse</t>
+          <t>metodologia
+forse</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
@@ -1298,457 +1402,548 @@
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi disciplinari
+risoluzione computazionale dei problemi</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi disciplinari
+risoluzione computazionale dei problemi</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi disciplinari
+risoluzione computazionale dei problemi</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (generica)</t>
+          <t>obiettivi disciplinari
+programmazione (generica)</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- logica</t>
+          <t>obiettivi pertinenti
+logica</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (generica)</t>
+          <t>obiettivi disciplinari
+programmazione (generica)</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi disciplinari
+risoluzione computazionale dei problemi</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- verifica/ correzione</t>
+          <t>obiettivi disciplinari
+verifica/ correzione</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- pratiche</t>
+          <t>obiettivi disciplinari
+pratiche</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- intelligenza artificiale</t>
+          <t>obiettivi disciplinari
+intelligenza artificiale</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- metodi</t>
+          <t>obiettivi disciplinari
+metodi</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- progettazione</t>
+          <t>obiettivi pertinenti
+progettazione</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- pratiche</t>
+          <t>obiettivi disciplinari
+pratiche</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- intelligenza artificiale</t>
+          <t>obiettivi disciplinari
+intelligenza artificiale</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- pratiche</t>
+          <t>obiettivi disciplinari
+pratiche</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>risposta generica d2 -- vuoto-d2</t>
+          <t>risposta generica d2
+vuoto-d2</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>risposta generica d2 -- generico-d2</t>
+          <t>risposta generica d2
+generico-d2</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>focus d2 -- studente</t>
+          <t>focus d2
+studente</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>focus d2 -- insegnante</t>
+          <t>focus d2
+insegnante</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>focus d2 -- contenuto</t>
+          <t>focus d2
+contenuto</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività digitale</t>
+          <t>obiettivi pertinenti
+creatività digitale</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>attività -- uso tecnologia e sviluppo contenuti</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività digitale</t>
+          <t>obiettivi pertinenti
+creatività digitale</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività</t>
+          <t>soft skills/ trasversali/ metacognizione
+creatività</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- logica</t>
+          <t>obiettivi pertinenti
+logica</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- progettazione e sviluppo oggetti</t>
+          <t>obiettivi pertinenti
+progettazione e sviluppo oggetti</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="FL2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- progettazione e sviluppo oggetti</t>
+          <t>obiettivi pertinenti
+progettazione e sviluppo oggetti</t>
         </is>
       </c>
       <c r="FM2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="FN2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="FO2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="FP2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- spazialità</t>
+          <t>interdisciplinarità
+spazialità</t>
         </is>
       </c>
       <c r="FQ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="FR2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="FS2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività</t>
+          <t>soft skills/ trasversali/ metacognizione
+creatività</t>
         </is>
       </c>
       <c r="FT2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="FU2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- progettazione e sviluppo oggetti</t>
+          <t>obiettivi pertinenti
+progettazione e sviluppo oggetti</t>
         </is>
       </c>
       <c r="FV2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="FW2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- progettazione e sviluppo oggetti</t>
+          <t>obiettivi pertinenti
+progettazione e sviluppo oggetti</t>
         </is>
       </c>
       <c r="FX2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- progettazione e sviluppo oggetti</t>
+          <t>obiettivi pertinenti
+progettazione e sviluppo oggetti</t>
         </is>
       </c>
       <c r="FY2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="FZ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- interdisciplinarità</t>
+          <t>interdisciplinarità
+interdisciplinarità</t>
         </is>
       </c>
       <c r="GA2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="GB2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="GC2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="GD2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="GE2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- relazionale-sociale</t>
+          <t>soft skills/ trasversali/ metacognizione
+relazionale-sociale</t>
         </is>
       </c>
       <c r="GF2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="GG2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="GH2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="GI2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="GJ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="GK2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="GL2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="GM2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- ragionamento</t>
+          <t>soft skills/ trasversali/ metacognizione
+ragionamento</t>
         </is>
       </c>
       <c r="GN2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="GO2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="GP2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="GQ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività</t>
+          <t>soft skills/ trasversali/ metacognizione
+creatività</t>
         </is>
       </c>
       <c r="GR2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- progettazione</t>
+          <t>obiettivi pertinenti
+progettazione</t>
         </is>
       </c>
       <c r="GS2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- pratiche</t>
+          <t>obiettivi disciplinari
+pratiche</t>
         </is>
       </c>
       <c r="GT2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="GU2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- progettazione</t>
+          <t>obiettivi pertinenti
+progettazione</t>
         </is>
       </c>
       <c r="GV2" t="inlineStr">
@@ -1763,502 +1958,602 @@
       </c>
       <c r="GX2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="GY2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="GZ2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="HA2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HB2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- relazionale-sociale</t>
+          <t>soft skills/ trasversali/ metacognizione
+relazionale-sociale</t>
         </is>
       </c>
       <c r="HC2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>obiettivi pertinenti
+logica</t>
         </is>
       </c>
       <c r="HD2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="HE2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="HF2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HG2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HH2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HI2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HJ2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HK2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HL2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività</t>
+          <t>soft skills/ trasversali/ metacognizione
+creatività</t>
         </is>
       </c>
       <c r="HM2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HN2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="HO2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HP2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HQ2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="HR2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- collaborazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+collaborazione</t>
         </is>
       </c>
       <c r="HS2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HT2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="HU2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="HV2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HW2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HX2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- empowerment</t>
+          <t>soft skills/ trasversali/ metacognizione
+empowerment</t>
         </is>
       </c>
       <c r="HY2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="HZ2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="IA2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="IB2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- relazionale-sociale</t>
+          <t>soft skills/ trasversali/ metacognizione
+relazionale-sociale</t>
         </is>
       </c>
       <c r="IC2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="ID2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- relazionale-sociale</t>
+          <t>soft skills/ trasversali/ metacognizione
+relazionale-sociale</t>
         </is>
       </c>
       <c r="IE2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="IF2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- processi cognitivi</t>
+          <t>soft skills/ trasversali/ metacognizione
+processi cognitivi</t>
         </is>
       </c>
       <c r="IG2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="IH2" t="inlineStr">
         <is>
-          <t>obiettivi pertinenti -- problem solving</t>
+          <t>obiettivi pertinenti
+problem solving</t>
         </is>
       </c>
       <c r="II2" t="inlineStr">
         <is>
-          <t>soft skills e metacognizione -- relazionale-sociale</t>
+          <t>soft skills/ trasversali/ metacognizione
+relazionale-sociale</t>
         </is>
       </c>
       <c r="IJ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- educazione fisica</t>
+          <t>interdisciplinarità
+educazione fisica</t>
         </is>
       </c>
       <c r="IK2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="IL2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- scienze</t>
+          <t>interdisciplinarità
+scienze</t>
         </is>
       </c>
       <c r="IM2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="IN2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- tecnologia</t>
+          <t>interdisciplinarità
+tecnologia</t>
         </is>
       </c>
       <c r="IO2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- spazialità</t>
+          <t>interdisciplinarità
+spazialità</t>
         </is>
       </c>
       <c r="IP2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="IQ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- spazialità</t>
+          <t>interdisciplinarità
+spazialità</t>
         </is>
       </c>
       <c r="IR2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="IS2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- lingua straniera</t>
+          <t>interdisciplinarità
+lingua straniera</t>
         </is>
       </c>
       <c r="IT2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="IU2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="IV2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="IW2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="IX2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- tecnologia</t>
+          <t>interdisciplinarità
+tecnologia</t>
         </is>
       </c>
       <c r="IY2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- geografia</t>
+          <t>interdisciplinarità
+geografia</t>
         </is>
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="JA2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="JB2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="JC2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- educazione civica</t>
+          <t>interdisciplinarità
+educazione civica</t>
         </is>
       </c>
       <c r="JD2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- interdisciplinarità</t>
+          <t>interdisciplinarità
+interdisciplinarità</t>
         </is>
       </c>
       <c r="JE2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- storia</t>
+          <t>interdisciplinarità
+storia</t>
         </is>
       </c>
       <c r="JF2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="JG2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- matematica</t>
+          <t>interdisciplinarità
+matematica</t>
         </is>
       </c>
       <c r="JH2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- scienze</t>
+          <t>interdisciplinarità
+scienze</t>
         </is>
       </c>
       <c r="JI2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività digitale</t>
+          <t>obiettivi pertinenti
+creatività digitale</t>
         </is>
       </c>
       <c r="JJ2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- scienze</t>
+          <t>interdisciplinarità
+scienze</t>
         </is>
       </c>
       <c r="JK2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="JL2" t="inlineStr">
         <is>
-          <t>interdisciplinarità -- italiano</t>
+          <t>interdisciplinarità
+italiano</t>
         </is>
       </c>
       <c r="JM2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="JN2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="JO2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="JP2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="JQ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="JR2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="JS2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- rappresentazione dell’informazione</t>
+          <t>obiettivi disciplinari
+rappresentazione dell'informazione</t>
         </is>
       </c>
       <c r="JT2" t="inlineStr">
         <is>
-          <t>abilità strumentali digitali -- uso di strumenti digitali</t>
+          <t>abilità strumentali digitali
+uso di strumenti digitali</t>
         </is>
       </c>
       <c r="JU2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- risoluzione computazionale dei problemi</t>
+          <t>obiettivi disciplinari
+risoluzione computazionale dei problemi</t>
         </is>
       </c>
       <c r="JV2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="JW2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="JX2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- algoritmica</t>
+          <t>obiettivi disciplinari
+algoritmica</t>
         </is>
       </c>
       <c r="JY2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- rappresentazione dell’informazione</t>
+          <t>obiettivi disciplinari
+rappresentazione dell'informazione</t>
         </is>
       </c>
       <c r="JZ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (generica)</t>
+          <t>obiettivi disciplinari
+programmazione (generica)</t>
         </is>
       </c>
       <c r="KA2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- consapevolezza digitale</t>
+          <t>obiettivi disciplinari
+consapevolezza digitale</t>
         </is>
       </c>
       <c r="KB2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="KC2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (generica)</t>
+          <t>obiettivi disciplinari
+programmazione (generica)</t>
         </is>
       </c>
       <c r="KD2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="KE2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- metodi</t>
+          <t>obiettivi disciplinari
+metodi</t>
         </is>
       </c>
       <c r="KF2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- rappresentazione dell’informazione</t>
+          <t>obiettivi disciplinari
+rappresentazione dell'informazione</t>
         </is>
       </c>
       <c r="KG2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="KH2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="KI2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="KJ2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- rappresentazione dell’informazione</t>
+          <t>obiettivi disciplinari
+rappresentazione dell'informazione</t>
         </is>
       </c>
       <c r="KK2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- creatività digitale</t>
+          <t>obiettivi pertinenti
+creatività digitale</t>
         </is>
       </c>
       <c r="KL2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- verifica/ correzione</t>
+          <t>obiettivi disciplinari
+verifica/ correzione</t>
         </is>
       </c>
       <c r="KM2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- generico</t>
+          <t>obiettivi disciplinari
+generico</t>
         </is>
       </c>
       <c r="KN2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="KO2" t="inlineStr">
         <is>
-          <t>obiettivi trasversali -- comunicazione</t>
+          <t>soft skills/ trasversali/ metacognizione
+comunicazione</t>
         </is>
       </c>
       <c r="KP2" t="inlineStr">
         <is>
-          <t>obiettivi disciplinari -- programmazione (specifici)</t>
+          <t>obiettivi disciplinari
+programmazione (specifici)</t>
         </is>
       </c>
       <c r="KQ2" t="inlineStr">
         <is>
-          <t>risposta generica d3 -- vuoto-d3</t>
+          <t>risposta generica d3
+vuoto-d3</t>
         </is>
       </c>
       <c r="KR2" t="inlineStr">
         <is>
-          <t>risposta generica d3 -- generico-d3</t>
+          <t>risposta generica d3
+generico-d3</t>
         </is>
       </c>
       <c r="KS2" t="inlineStr">
         <is>
-          <t>risposta generica d3 -- copia risposta 2</t>
+          <t>risposta generica d3
+copia risposta 2</t>
         </is>
       </c>
     </row>
